--- a/output/pdf_financials_xlsx/TERA.xlsx
+++ b/output/pdf_financials_xlsx/TERA.xlsx
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.947895</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.814871</v>
       </c>
       <c r="D92" s="1" t="inlineStr">
         <is>
@@ -2468,10 +2468,10 @@
         <v>0</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-0.358563</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-0.800187</v>
       </c>
     </row>
     <row r="119">
@@ -5804,7 +5804,11 @@
           <t>Deferred exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TERA.xlsx
+++ b/output/pdf_financials_xlsx/TERA.xlsx
@@ -621,7 +621,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000298</v>
       </c>
     </row>
     <row r="13">
@@ -885,7 +885,7 @@
         <v>-0.982779</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.76303</v>
+        <v>-0.763328</v>
       </c>
     </row>
     <row r="28">
@@ -917,7 +917,7 @@
         <v>-0.982779</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.76303</v>
+        <v>-0.763328</v>
       </c>
     </row>
     <row r="30">
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.020321</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.000563</v>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.020321</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.000563</v>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.073147</v>
+        <v>0.052826</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.011912</v>
+        <v>0.011349</v>
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">

--- a/output/pdf_financials_xlsx/TERA.xlsx
+++ b/output/pdf_financials_xlsx/TERA.xlsx
@@ -2353,7 +2353,7 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>0.01054</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.01054</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
@@ -2743,7 +2743,7 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-0.638578</v>
+        <v>-0.649118</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>-0.672995</v>
@@ -6017,7 +6017,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E108" s="5" t="n">
         <v>0.01054</v>
       </c>
@@ -6201,7 +6205,11 @@
           <t>Proceeds from share issuance</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E114" s="5" t="n">
         <v>1.424976</v>
       </c>
